--- a/data/trans_camb/P1429-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1429-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,51</t>
         </is>
       </c>
     </row>
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; -0,2</t>
+          <t>-2,07; -0,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; -0,19</t>
+          <t>-1,96; -0,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,9</t>
+          <t>-0,99; 3,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>-0,96; -0,09</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>-0,95; -0,1</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-0,95; -0,1</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,77</t>
+          <t>-0,38; 2,69</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>150,4%</t>
+          <t>134,35%</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; -0,14</t>
+          <t>-1,62; -0,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; -0,14</t>
+          <t>-1,61; -0,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; -0,14</t>
+          <t>-1,69; -0,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,58</t>
+          <t>-0,33; 1,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,0</t>
+          <t>-0,95; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,0</t>
+          <t>-1,11; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,47</t>
+          <t>-0,63; 0,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; -0,15</t>
+          <t>-1,09; -0,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; -0,15</t>
+          <t>-1,14; -0,16</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 347,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,0</t>
+          <t>-1,18; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,14</t>
+          <t>-0,87; 0,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,85</t>
+          <t>-0,52; 0,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,13</t>
+          <t>-1,33; 0,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,56</t>
+          <t>-1,05; 0,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,26</t>
+          <t>-1,36; 0,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; -0,05</t>
+          <t>-0,95; -0,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,25</t>
+          <t>-0,73; 0,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,3</t>
+          <t>-0,78; 0,21</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-57,69%</t>
+          <t>-61,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-35,14%</t>
+          <t>-40,69%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 113,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,44; 245,62</t>
+          <t>-86,61; 196,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 151,14</t>
+          <t>-100,0; 99,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 76,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,8; 104,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-85,33; 145,87</t>
+          <t>-86,38; 110,04</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,32</t>
+          <t>-1,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,33</t>
+          <t>-0,89; 0,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,68</t>
+          <t>-0,72; 0,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,51</t>
+          <t>-0,63; 0,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,3</t>
+          <t>-2,44; 1,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -0,15</t>
+          <t>-3,53; -0,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; -0,03</t>
+          <t>-3,0; 0,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,6</t>
+          <t>-1,39; 0,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,09</t>
+          <t>-1,82; -0,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,08</t>
+          <t>-1,48; 0,21</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-14,6%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-47,97%</t>
+          <t>-40,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-48,1%</t>
+          <t>-33,87%</t>
         </is>
       </c>
     </row>
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-62,98; 78,83</t>
+          <t>-65,95; 71,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,78; 5,89</t>
+          <t>-86,11; 7,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,22; 5,61</t>
+          <t>-71,31; 22,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-68,54; 60,3</t>
+          <t>-65,01; 81,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,07; 21,98</t>
+          <t>-83,25; 10,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,88; 9,31</t>
+          <t>-67,79; 27,11</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-1,07</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-1,93</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,55</t>
+          <t>-1,59</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -0,51</t>
+          <t>-3,55; -0,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,44; -0,26</t>
+          <t>-3,42; -0,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,48</t>
+          <t>-2,97; 0,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 3,37</t>
+          <t>-4,5; 2,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,04; -0,36</t>
+          <t>-7,55; -0,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 0,93</t>
+          <t>-5,49; 1,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,95</t>
+          <t>-3,33; 1,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,72; -0,92</t>
+          <t>-4,85; -0,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 0,15</t>
+          <t>-3,48; 0,07</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-48,66%</t>
+          <t>-54,36%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-22,64%</t>
+          <t>-22,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-29,44%</t>
+          <t>-30,05%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; -14,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 46,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,02; 65,92</t>
+          <t>-86,64; 75,54</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 57,37</t>
+          <t>-43,12; 44,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-68,72; -1,98</t>
+          <t>-71,84; -6,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 15,73</t>
+          <t>-49,37; 19,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,05; 24,06</t>
+          <t>-50,38; 26,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-72,82; -19,49</t>
+          <t>-71,95; -19,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-52,43; 3,87</t>
+          <t>-51,61; 1,76</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-1,29</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-5,15</t>
+          <t>-1,67</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,91</t>
+          <t>-1,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,86; -0,82</t>
+          <t>-4,94; -0,91</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,29; -1,43</t>
+          <t>-5,07; -1,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,56</t>
+          <t>-3,6; 0,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 1,46</t>
+          <t>-7,98; 1,24</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 4,33</t>
+          <t>-5,21; 4,16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,42; -0,41</t>
+          <t>-5,92; 2,21</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,39; -0,07</t>
+          <t>-5,53; -0,15</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,95</t>
+          <t>-4,29; 1,05</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,3; -0,38</t>
+          <t>-4,07; 0,72</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-42,92%</t>
+          <t>-45,19%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-43,28%</t>
+          <t>-14,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-37,65%</t>
+          <t>-21,58%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-100,0; 7,75</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-78,09; 61,35</t>
+          <t>-78,48; 48,83</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-53,73; 15,38</t>
+          <t>-53,38; 14,43</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-33,82; 45,72</t>
+          <t>-37,03; 42,48</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-77,55; -2,95</t>
+          <t>-39,55; 22,48</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-57,77; 1,34</t>
+          <t>-60,88; -0,53</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-49,88; 13,46</t>
+          <t>-46,92; 16,92</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-70,28; -7,91</t>
+          <t>-42,91; 11,92</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,98</t>
+          <t>-1,85</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 0,42</t>
+          <t>-6,86; -0,1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 0,59</t>
+          <t>-5,42; 1,18</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 1,1</t>
+          <t>-5,61; 1,04</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 6,04</t>
+          <t>-4,8; 6,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 2,97</t>
+          <t>-7,24; 3,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 7,17</t>
+          <t>-2,0; 7,32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 2,43</t>
+          <t>-4,56; 2,44</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 0,95</t>
+          <t>-6,19; 0,86</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 3,74</t>
+          <t>-2,7; 3,73</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-41,64%</t>
+          <t>-38,94%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 58,15</t>
+          <t>-100,0; 53,11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-83,0; 33,43</t>
+          <t>-81,6; 71,9</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-74,86; 45,23</t>
+          <t>-76,27; 49,99</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-29,55; 59,8</t>
+          <t>-28,92; 58,9</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-48,56; 27,57</t>
+          <t>-45,65; 30,22</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 71,34</t>
+          <t>-11,87; 70,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 31,67</t>
+          <t>-38,72; 29,55</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-49,41; 11,3</t>
+          <t>-50,62; 13,04</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 46,77</t>
+          <t>-21,39; 44,98</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,16</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; -0,45</t>
+          <t>-1,25; -0,5</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,12; -0,31</t>
+          <t>-1,11; -0,32</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,28</t>
+          <t>-0,68; 0,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,72</t>
+          <t>-1,32; 0,79</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,12</t>
+          <t>-1,73; 0,18</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,97</t>
+          <t>-0,45; 1,39</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,19; -0,05</t>
+          <t>-1,04; -0,05</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,33; -0,24</t>
+          <t>-1,25; -0,25</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,48</t>
+          <t>-0,4; 0,67</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-20,56%</t>
+          <t>-18,92%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-1,21%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-94,18; -46,04</t>
+          <t>-94,18; -45,69</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-84,58; -37,68</t>
+          <t>-84,24; -37,78</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 39,75</t>
+          <t>-52,1; 37,53</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 19,04</t>
+          <t>-27,57; 20,5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 3,73</t>
+          <t>-36,49; 5,0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 25,27</t>
+          <t>-9,18; 38,63</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-39,21; -1,65</t>
+          <t>-35,85; -1,22</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-43,88; -10,37</t>
+          <t>-42,02; -10,49</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 20,06</t>
+          <t>-13,4; 29,4</t>
         </is>
       </c>
     </row>
